--- a/branches/review-laborbefund-2027/ValueSet-mii-vs-labor-identifier-type-codes.xlsx
+++ b/branches/review-laborbefund-2027/ValueSet-mii-vs-labor-identifier-type-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:10:25+00:00</t>
+    <t>2026-09-08T11:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
